--- a/event_feedback_forms/017_post_event_innovation_survey--event_feedback_forms.xlsx
+++ b/event_feedback_forms/017_post_event_innovation_survey--event_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,8 +1056,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'great_idea!',_'value':_5}</t>
+          <t>great_idea!</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Great idea!', 'value': 5}</t>
+          <t>Great idea!</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'not_so_great',_'value':_1}</t>
+          <t>not_so_great</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Not so great', 'value': 1}</t>
+          <t>Not so great</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'not_innovative_at_all',_'value':_1}</t>
+          <t>not_innovative_at_all</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Not innovative at all', 'value': 1}</t>
+          <t>Not innovative at all</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'neutral',_'value':_3}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Neutral', 'value': 3}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'not_sure',_'value':_0}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Not sure', 'value': 0}</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'great_idea!',_'value':_5}</t>
+          <t>great_idea!</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Great idea!', 'value': 5}</t>
+          <t>Great idea!</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'not_so_great',_'value':_1}</t>
+          <t>not_so_great</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Not so great', 'value': 1}</t>
+          <t>Not so great</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'not_innovative_at_all',_'value':_1}</t>
+          <t>not_innovative_at_all</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Not innovative at all', 'value': 1}</t>
+          <t>Not innovative at all</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'neutral',_'value':_3}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Neutral', 'value': 3}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_25,_'label':_'not_sure',_'value':_0}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 25, 'label': 'Not sure', 'value': 0}</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_31,_'label':_'will_follow_up',_'value':_'will_follow_up'}</t>
+          <t>will_follow_up</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 31, 'label': 'Will follow up', 'value': 'Will follow up'}</t>
+          <t>Will follow up</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_32,_'label':_'not_now',_'value':_'not_now'}</t>
+          <t>not_now</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 32, 'label': 'Not now', 'value': 'Not now'}</t>
+          <t>Not now</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_41,_'label':_'conference',_'value':_'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 41, 'label': 'Conference', 'value': 'Conference'}</t>
+          <t>Conference</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_42,_'label':_'workshop',_'value':_'workshop'}</t>
+          <t>workshop</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 42, 'label': 'Workshop', 'value': 'Workshop'}</t>
+          <t>Workshop</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_43,_'label':_'program',_'value':_'program'}</t>
+          <t>program</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 43, 'label': 'Program', 'value': 'Program'}</t>
+          <t>Program</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_51,_'label':_1,_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 51, 'label': 1, 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_52,_'label':_2,_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 52, 'label': 2, 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_53,_'label':_3,_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 53, 'label': 3, 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_54,_'label':_4,_'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 54, 'label': 4, 'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_55,_'label':_5,_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 55, 'label': 5, 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_61,_'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 61, 'label': 'Excellent', 'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_62,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 62, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_63,_'label':_'okay',_'value':_'okay'}</t>
+          <t>okay</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 63, 'label': 'Okay', 'value': 'Okay'}</t>
+          <t>Okay</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_64,_'label':_'bad',_'value':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 64, 'label': 'Bad', 'value': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_65,_'label':_'not_at_all',_'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 65, 'label': 'Not at all', 'value': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_71,_'label':_'very_important',_'value':_3}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 71, 'label': 'Very important', 'value': 3}</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_72,_'label':_'not_very_important',_'value':_1}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 72, 'label': 'Not very important', 'value': 1}</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_73,_'label':_'not_at_all_important',_'value':_1}</t>
+          <t>not_at_all_important</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 73, 'label': 'Not at all important', 'value': 1}</t>
+          <t>Not at all important</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_74,_'label':_'very_unimportant',_'value':_0}</t>
+          <t>very_unimportant</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 74, 'label': 'Very unimportant', 'value': 0}</t>
+          <t>Very unimportant</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1578,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_81,_'label':_'will_follow_up',_'value':_'will_follow_up'}</t>
+          <t>will_follow_up</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 81, 'label': 'Will follow up', 'value': 'Will follow up'}</t>
+          <t>Will follow up</t>
         </is>
       </c>
     </row>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_82,_'label':_'not_now',_'value':_'not_now'}</t>
+          <t>not_now</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 82, 'label': 'Not now', 'value': 'Not now'}</t>
+          <t>Not now</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_91,_'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 91, 'label': 'Email', 'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1629,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_92,_'label':_'phone_call',_'value':_'phone_call'}</t>
+          <t>phone_call</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 92, 'label': 'Phone call', 'value': 'Phone call'}</t>
+          <t>Phone call</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_93,_'label':_'in-person',_'value':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 93, 'label': 'In-person', 'value': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_94,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 94, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_101,_'label':_'once_a_week',_'value':_1}</t>
+          <t>once_a_week</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 101, 'label': 'Once a week', 'value': 1}</t>
+          <t>Once a week</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_102,_'label':_'once_a_month',_'value':_2}</t>
+          <t>once_a_month</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 102, 'label': 'Once a month', 'value': 2}</t>
+          <t>Once a month</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_103,_'label':_'once_a_quarter',_'value':_3}</t>
+          <t>once_a_quarter</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 103, 'label': 'Once a quarter', 'value': 3}</t>
+          <t>Once a quarter</t>
         </is>
       </c>
     </row>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_104,_'label':_'once_a_year',_'value':_4}</t>
+          <t>once_a_year</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 104, 'label': 'Once a year', 'value': 4}</t>
+          <t>Once a year</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_105,_'label':_'never',_'value':_0}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 105, 'label': 'Never', 'value': 0}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
